--- a/restaurant_crawler/restaurant_data_台北_海鮮料理_20250910_192738_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_海鮮料理_20250910_192738_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB85E75A-067F-424E-A25A-4EC8D90E4712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A5221F-852C-4164-9618-0EF003AA31B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="305">
   <si>
     <t>name</t>
   </si>
@@ -439,18 +439,6 @@
     <t>ChIJ0XJmC8WrQjQRIj00MmTv7ZY</t>
   </si>
   <si>
-    <t>新東南海鮮餐廳 松山店</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區八德路四段656號</t>
-  </si>
-  <si>
-    <t>02 2748 9966</t>
-  </si>
-  <si>
-    <t>ChIJdzQ9rLGrQjQR6J-Nix7QAO8</t>
-  </si>
-  <si>
     <t>海世界活海鮮餐廳</t>
   </si>
   <si>
@@ -794,21 +782,6 @@
   </si>
   <si>
     <t>ChIJN1jwM0OpQjQRfbLOPkAmOhc</t>
-  </si>
-  <si>
-    <t>吉品海鮮餐廳 信義店</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安区信义路四段236號三商美邦宏远大楼2樓</t>
-  </si>
-  <si>
-    <t>02 2700 3311</t>
-  </si>
-  <si>
-    <t>http://www.jipin.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJDwI5a8yrQjQR76BWieGKPjY</t>
   </si>
   <si>
     <t>漉 海鮮蒸氣鍋-松江店</t>
@@ -1554,28 +1527,28 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>151</v>
       </c>
       <c r="E8">
-        <v>4.4000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="F8">
-        <v>7672</v>
+        <v>3814</v>
       </c>
       <c r="G8" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="I8" t="s">
         <v>26</v>
@@ -1583,28 +1556,28 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>154</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>155</v>
+        <v>200</v>
       </c>
       <c r="E9">
-        <v>4.8</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F9">
-        <v>3814</v>
+        <v>741</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="I9" t="s">
         <v>26</v>
@@ -1612,28 +1585,28 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="E10">
-        <v>4.9000000000000004</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F10">
-        <v>741</v>
+        <v>1132</v>
       </c>
       <c r="G10" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="H10" t="s">
-        <v>206</v>
+        <v>237</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
@@ -1641,28 +1614,28 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E11">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="F11">
-        <v>1132</v>
+        <v>582</v>
       </c>
       <c r="G11" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="H11" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1670,28 +1643,28 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F12">
-        <v>582</v>
+        <v>1853</v>
       </c>
       <c r="G12" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="H12" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1699,88 +1672,30 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="C13" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
       <c r="E13">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F13">
-        <v>1957</v>
+        <v>1680</v>
       </c>
       <c r="G13" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" t="s">
-        <v>265</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E14">
-        <v>4.3</v>
-      </c>
-      <c r="F14">
-        <v>1853</v>
-      </c>
-      <c r="G14" t="s">
-        <v>267</v>
-      </c>
-      <c r="H14" t="s">
-        <v>268</v>
-      </c>
-      <c r="I14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>304</v>
-      </c>
-      <c r="C15" t="s">
-        <v>305</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E15">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F15">
-        <v>1680</v>
-      </c>
-      <c r="G15" t="s">
-        <v>307</v>
-      </c>
-      <c r="H15" t="s">
-        <v>308</v>
-      </c>
-      <c r="I15" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2271,13 +2186,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E35">
         <v>4.4000000000000004</v>
@@ -2286,7 +2201,7 @@
         <v>554</v>
       </c>
       <c r="G35" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -2294,16 +2209,16 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E36">
         <v>4.3</v>
@@ -2312,7 +2227,7 @@
         <v>657</v>
       </c>
       <c r="G36" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -2320,16 +2235,16 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E37">
         <v>4.5999999999999996</v>
@@ -2338,7 +2253,7 @@
         <v>720</v>
       </c>
       <c r="G37" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2346,16 +2261,16 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C38" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>4.4000000000000004</v>
@@ -2364,7 +2279,7 @@
         <v>854</v>
       </c>
       <c r="G38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2372,16 +2287,16 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E39">
         <v>4.0999999999999996</v>
@@ -2390,7 +2305,7 @@
         <v>4369</v>
       </c>
       <c r="G39" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2398,13 +2313,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B40" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E40">
         <v>4.0999999999999996</v>
@@ -2413,7 +2328,7 @@
         <v>1707</v>
       </c>
       <c r="G40" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
@@ -2421,16 +2336,16 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B41" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D41" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E41">
         <v>4.3</v>
@@ -2439,7 +2354,7 @@
         <v>380</v>
       </c>
       <c r="G41" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -2447,13 +2362,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B42" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E42">
         <v>4.3</v>
@@ -2462,7 +2377,7 @@
         <v>849</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
@@ -2470,16 +2385,16 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C43" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D43" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E43">
         <v>4.3</v>
@@ -2488,7 +2403,7 @@
         <v>658</v>
       </c>
       <c r="G43" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -2496,16 +2411,16 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D44" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E44">
         <v>4.2</v>
@@ -2514,7 +2429,7 @@
         <v>2112</v>
       </c>
       <c r="G44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -2522,16 +2437,16 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C45" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D45" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E45">
         <v>4.8</v>
@@ -2540,7 +2455,7 @@
         <v>472</v>
       </c>
       <c r="G45" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -2548,16 +2463,16 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E46">
         <v>4.5999999999999996</v>
@@ -2566,7 +2481,7 @@
         <v>1073</v>
       </c>
       <c r="G46" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
@@ -2574,13 +2489,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E47">
         <v>4.5</v>
@@ -2589,7 +2504,7 @@
         <v>258</v>
       </c>
       <c r="G47" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I47" t="s">
         <v>14</v>
@@ -2597,16 +2512,16 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B48" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D48" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E48">
         <v>4.4000000000000004</v>
@@ -2615,7 +2530,7 @@
         <v>1560</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I48" t="s">
         <v>14</v>
@@ -2623,16 +2538,16 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C49" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D49" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E49">
         <v>4.4000000000000004</v>
@@ -2641,7 +2556,7 @@
         <v>301</v>
       </c>
       <c r="G49" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I49" t="s">
         <v>14</v>
@@ -2649,16 +2564,16 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C50" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D50" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E50">
         <v>4</v>
@@ -2667,7 +2582,7 @@
         <v>3472</v>
       </c>
       <c r="G50" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I50" t="s">
         <v>14</v>
@@ -2675,16 +2590,16 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E51">
         <v>4</v>
@@ -2693,7 +2608,7 @@
         <v>2248</v>
       </c>
       <c r="G51" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I51" t="s">
         <v>14</v>
@@ -2701,16 +2616,16 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D52" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E52">
         <v>4.7</v>
@@ -2719,7 +2634,7 @@
         <v>1145</v>
       </c>
       <c r="G52" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I52" t="s">
         <v>14</v>
@@ -2727,16 +2642,16 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B53" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C53" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D53" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E53">
         <v>4.0999999999999996</v>
@@ -2745,7 +2660,7 @@
         <v>1922</v>
       </c>
       <c r="G53" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="I53" t="s">
         <v>14</v>
@@ -2753,13 +2668,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="E54">
         <v>4.2</v>
@@ -2768,7 +2683,7 @@
         <v>934</v>
       </c>
       <c r="G54" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="I54" t="s">
         <v>14</v>
@@ -2776,16 +2691,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C55" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="E55">
         <v>4.3</v>
@@ -2794,7 +2709,7 @@
         <v>1058</v>
       </c>
       <c r="G55" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="I55" t="s">
         <v>14</v>
@@ -2802,16 +2717,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B56" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C56" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="D56" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="E56">
         <v>4.8</v>
@@ -2820,7 +2735,7 @@
         <v>952</v>
       </c>
       <c r="G56" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="I56" t="s">
         <v>14</v>
@@ -2828,16 +2743,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B57" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C57" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="D57" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E57">
         <v>4.2</v>
@@ -2846,7 +2761,7 @@
         <v>4908</v>
       </c>
       <c r="G57" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="I57" t="s">
         <v>14</v>
@@ -2854,16 +2769,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B58" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C58" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D58" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E58">
         <v>4.4000000000000004</v>
@@ -2872,7 +2787,7 @@
         <v>632</v>
       </c>
       <c r="G58" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="I58" t="s">
         <v>14</v>
@@ -2880,16 +2795,16 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="B59" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C59" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D59" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -2898,7 +2813,7 @@
         <v>1701</v>
       </c>
       <c r="G59" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="I59" t="s">
         <v>14</v>
@@ -2906,16 +2821,16 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C60" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D60" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E60">
         <v>4.2</v>
@@ -2924,7 +2839,7 @@
         <v>946</v>
       </c>
       <c r="G60" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="I60" t="s">
         <v>14</v>
@@ -2932,16 +2847,16 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B61" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C61" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D61" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="E61">
         <v>4.0999999999999996</v>
@@ -2950,7 +2865,7 @@
         <v>1272</v>
       </c>
       <c r="G61" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="I61" t="s">
         <v>14</v>

--- a/restaurant_crawler/restaurant_data_台北_海鮮料理_20250910_192738_with_emails.xlsx
+++ b/restaurant_crawler/restaurant_data_台北_海鮮料理_20250910_192738_with_emails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slow3\OneDrive\桌面\GitHubProjects\BYOB\restaurant_crawler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A5221F-852C-4164-9618-0EF003AA31B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E1AD33-50EE-43F9-905A-53A9E35A8750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="239">
   <si>
     <t>name</t>
   </si>
@@ -67,21 +67,6 @@
     <t>not_found</t>
   </si>
   <si>
-    <t>VG the Seafood Bar</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安区敦化南路二段11巷6號1樓</t>
-  </si>
-  <si>
-    <t>0905 576 068</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/-LnkZeNwebenIIVt3LYy:inline-live-1/-LnkZeRwaPb_Q5JYjIl5</t>
-  </si>
-  <si>
-    <t>ChIJ1SEboM2rQjQR7qAUBryB_9U</t>
-  </si>
-  <si>
     <t>真的好海鮮餐廳</t>
   </si>
   <si>
@@ -97,9 +82,6 @@
     <t>ChIJV8swk9urQjQR1ee_CCk2Si0</t>
   </si>
   <si>
-    <t>aec31088a6fb4f6eafac028a91e1cf21@o769852.ingest.sentry.io</t>
-  </si>
-  <si>
     <t>found</t>
   </si>
   <si>
@@ -127,9 +109,6 @@
     <t>02 2718 9319</t>
   </si>
   <si>
-    <t>https://linkbio.co/5060207XfX1Wq?utm_source=instabio&amp;utm_medium=share</t>
-  </si>
-  <si>
     <t>ChIJZxaW3SOrQjQRGzm1zwc6r2U</t>
   </si>
   <si>
@@ -151,18 +130,6 @@
     <t>info@elatedthemes.com</t>
   </si>
   <si>
-    <t>田園海鮮餐廳</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區八德路二段174巷5號</t>
-  </si>
-  <si>
-    <t>02 2781 5137</t>
-  </si>
-  <si>
-    <t>ChIJG-oEi9irQjQRe-BJfgoUMtw</t>
-  </si>
-  <si>
     <t>煮海 Tresors de la mer</t>
   </si>
   <si>
@@ -217,36 +184,6 @@
     <t>ccgh2323@gmail.com</t>
   </si>
   <si>
-    <t>海九澎湖海鮮餐廳</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區長安東路二段170號</t>
-  </si>
-  <si>
-    <t>02 2751 7272</t>
-  </si>
-  <si>
-    <t>http://www.hijo.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJC8Sm1d6rQjQRkybRsVasbvo</t>
-  </si>
-  <si>
-    <t>北海漁村 台北杭州店</t>
-  </si>
-  <si>
-    <t>100台灣台北市中正區杭州南路一段8號</t>
-  </si>
-  <si>
-    <t>02 2357 6188</t>
-  </si>
-  <si>
-    <t>http://www.fineseafood.com.tw/</t>
-  </si>
-  <si>
-    <t>ChIJAw7RiXqpQjQRG_fIayNUWBQ</t>
-  </si>
-  <si>
     <t>川郎活蟹海鮮料理</t>
   </si>
   <si>
@@ -280,21 +217,6 @@
     <t>mitsui.z600@msa.hinet.net</t>
   </si>
   <si>
-    <t>鱻活驛棧</t>
-  </si>
-  <si>
-    <t>104080台灣台北市中山區復興北路282號1樓</t>
-  </si>
-  <si>
-    <t>02 2518 1000</t>
-  </si>
-  <si>
-    <t>https://qr-official.line.me/gs/M_263owfnj_BW.png?oat_content=qr</t>
-  </si>
-  <si>
-    <t>ChIJU15UfrirQjQRpie1N-yanuA</t>
-  </si>
-  <si>
     <t>89海鮮</t>
   </si>
   <si>
@@ -319,36 +241,9 @@
     <t>02 2767 7058</t>
   </si>
   <si>
-    <t>https://reurl.cc/o0NQYQ</t>
-  </si>
-  <si>
     <t>ChIJ2TXdqL2rQjQR-CAqmFHAM9s</t>
   </si>
   <si>
-    <t>欣海岸海鮮料理</t>
-  </si>
-  <si>
-    <t>105台灣台北市松山區八德路三段158巷1-2號</t>
-  </si>
-  <si>
-    <t>0919 191 820</t>
-  </si>
-  <si>
-    <t>ChIJWVfyM4irQjQRhBwgmaLujLs</t>
-  </si>
-  <si>
-    <t>雙喜星海鮮</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區建國北路一段72號</t>
-  </si>
-  <si>
-    <t>02 2507 9909</t>
-  </si>
-  <si>
-    <t>ChIJNwyJ6gupQjQRTHERui7fWc4</t>
-  </si>
-  <si>
     <t>香港九記海鮮</t>
   </si>
   <si>
@@ -439,33 +334,6 @@
     <t>ChIJ0XJmC8WrQjQRIj00MmTv7ZY</t>
   </si>
   <si>
-    <t>海世界活海鮮餐廳</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區農安街122號</t>
-  </si>
-  <si>
-    <t>02 2593 0271</t>
-  </si>
-  <si>
-    <t>ChIJ0erkH1qpQjQRZnTghRueYS8</t>
-  </si>
-  <si>
-    <t>阿隆龜山島現撈海產</t>
-  </si>
-  <si>
-    <t>103台灣台北市大同區天水路51巷34號</t>
-  </si>
-  <si>
-    <t>0936 167 338</t>
-  </si>
-  <si>
-    <t>http://nickhow.tw/blog/post/459579334</t>
-  </si>
-  <si>
-    <t>ChIJB2-3aROpQjQRBDAlhFrqgQ8</t>
-  </si>
-  <si>
     <t>竹苑shabu</t>
   </si>
   <si>
@@ -529,18 +397,6 @@
     <t>ChIJ1aNM91upQjQR4b2RE-l0QpM</t>
   </si>
   <si>
-    <t>艋舺熱海 海鮮餐廳</t>
-  </si>
-  <si>
-    <t>108台灣台北市萬華區和平西路三段162號</t>
-  </si>
-  <si>
-    <t>02 2306 3797</t>
-  </si>
-  <si>
-    <t>ChIJU7cRla6pQjQRhchv-ZhGAis</t>
-  </si>
-  <si>
     <t>大鵬灣餐廳 DapengBay restaurant</t>
   </si>
   <si>
@@ -556,18 +412,6 @@
     <t>ChIJlxMXHHCpQjQRe-gv2tDCc6k</t>
   </si>
   <si>
-    <t>府岸台菜海鮮城</t>
-  </si>
-  <si>
-    <t>106台灣台北市大安區永康街8巷7號</t>
-  </si>
-  <si>
-    <t>02 2393 5901</t>
-  </si>
-  <si>
-    <t>ChIJHcGMToKpQjQRcWfGfKBrPIE</t>
-  </si>
-  <si>
     <t>華西街台南擔仔麵海鮮餐廳</t>
   </si>
   <si>
@@ -598,21 +442,6 @@
     <t>ChIJKazzDl2pQjQRFREJQvboxf0</t>
   </si>
   <si>
-    <t>艾里翁廚房</t>
-  </si>
-  <si>
-    <t>110051台灣台北市信義區松信路55號</t>
-  </si>
-  <si>
-    <t>0988 222 611</t>
-  </si>
-  <si>
-    <t>https://line.me/ti/g2/zy9tOwAKyo_3qqiT8wGPBYlm6b3V8qUCN2SZGQ?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default</t>
-  </si>
-  <si>
-    <t>ChIJ84V-r3erQjQR3SPZVqzpaYU</t>
-  </si>
-  <si>
     <t>三分半海鮮鍋物</t>
   </si>
   <si>
@@ -646,18 +475,6 @@
     <t>ChIJ68mpabOrQjQR9yHUJLnGRUM</t>
   </si>
   <si>
-    <t>九條楊海鮮</t>
-  </si>
-  <si>
-    <t>10491台灣台北市中山區南京東路一段132巷25號</t>
-  </si>
-  <si>
-    <t>02 2567 4706</t>
-  </si>
-  <si>
-    <t>ChIJb7vp32WpQjQRuBpAa86Lbvk</t>
-  </si>
-  <si>
     <t>明福台菜</t>
   </si>
   <si>
@@ -682,9 +499,6 @@
     <t>02 2523 5588</t>
   </si>
   <si>
-    <t>https://www.premium-no8.com/</t>
-  </si>
-  <si>
     <t>ChIJE_EfS2GpQjQRmAiwu1MgkCQ</t>
   </si>
   <si>
@@ -802,33 +616,6 @@
     <t>service@secar.com.tw</t>
   </si>
   <si>
-    <t>好小子海鮮店</t>
-  </si>
-  <si>
-    <t>104台灣台北市中山區林森北路305號</t>
-  </si>
-  <si>
-    <t>02 2537 2093</t>
-  </si>
-  <si>
-    <t>ChIJp8t44mepQjQReTRHDcIxHf0</t>
-  </si>
-  <si>
-    <t>【台北君悅酒店】漂亮廣式海鮮餐廳 Pearl Liang</t>
-  </si>
-  <si>
-    <t>110061台灣台北市信义区松寿路2號2F</t>
-  </si>
-  <si>
-    <t>02 2720 1230</t>
-  </si>
-  <si>
-    <t>https://www.hyatt.com/zh-HK/hotel/taiwan/grand-hyatt-taipei/taigh/dining?src=prop_misc_taigh_other_google-my-business_pearlliang</t>
-  </si>
-  <si>
-    <t>ChIJty1ap7erQjQRSqbaYk3H3qA</t>
-  </si>
-  <si>
     <t>南方漁場</t>
   </si>
   <si>
@@ -889,21 +676,6 @@
     <t>ChIJx4-0adyrQjQRwdP-8zBRCAk</t>
   </si>
   <si>
-    <t>Seafood &amp; Meat 波波海鮮市集-台北內湖活海鮮/龍蝦/帝王蟹/大閘蟹/螃蟹/生蠔 2025必吃海鮮餐廳 慶生/聚餐/包場/公司聚餐 人氣訂位熱門美食 PTT Dcard</t>
-  </si>
-  <si>
-    <t>114台灣台北市內湖區民權東路六段184-1號</t>
-  </si>
-  <si>
-    <t>02 8792 7474</t>
-  </si>
-  <si>
-    <t>https://inline.app/booking/seafoodnmeat/seafoodnmeat</t>
-  </si>
-  <si>
-    <t>ChIJ0axSXoytQjQRZ6KXXfPWfDI</t>
-  </si>
-  <si>
     <t>梅子台灣料理餐廳 林森老店</t>
   </si>
   <si>
@@ -919,9 +691,6 @@
     <t>ChIJO16aXm-pQjQR5OsC7hn8zKo</t>
   </si>
   <si>
-    <t>605a7baede844d278b89dc95ae0a9123@sentry-next.wixpress.com</t>
-  </si>
-  <si>
     <t>一代佳人海鮮碳烤</t>
   </si>
   <si>
@@ -935,6 +704,40 @@
   </si>
   <si>
     <t>ChIJre9cvoGpQjQRA3mn9UiYa0A</t>
+  </si>
+  <si>
+    <t>siseafood168@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/siseafood73</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.facebook.com/AIORockWorld</t>
+  </si>
+  <si>
+    <t>da.peng.bay@gmail.com</t>
+  </si>
+  <si>
+    <t>sv31@seafoodtaipei.com.tw</t>
+  </si>
+  <si>
+    <t>premium_sea_food@yahoo.com.tw</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100064150560715#</t>
+  </si>
+  <si>
+    <t>info@coca-hotpot.com</t>
+  </si>
+  <si>
+    <t>tainanseafood@gmail.com</t>
+  </si>
+  <si>
+    <t>taipei@reallygoodseafood.com</t>
+  </si>
+  <si>
+    <t>taipeiumeko@yahoo.com</t>
   </si>
 </sst>
 </file>
@@ -1005,12 +808,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1313,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.625" customWidth="1"/>
@@ -1322,7 +1126,7 @@
     <col min="9" max="9" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1351,18 +1155,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E2">
         <v>4.3</v>
@@ -1371,27 +1175,27 @@
         <v>1635</v>
       </c>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>237</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>4.5</v>
@@ -1400,27 +1204,27 @@
         <v>4352</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="E4">
         <v>4.2</v>
@@ -1429,27 +1233,27 @@
         <v>2548</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>4.3</v>
@@ -1458,27 +1262,27 @@
         <v>11817</v>
       </c>
       <c r="G5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="E6">
         <v>4.7</v>
@@ -1487,27 +1291,27 @@
         <v>431</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="E7">
         <v>4</v>
@@ -1516,27 +1320,27 @@
         <v>12626</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="I7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>4.8</v>
@@ -1545,27 +1349,27 @@
         <v>3814</v>
       </c>
       <c r="G8" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="H8" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="E9">
         <v>4.9000000000000004</v>
@@ -1574,27 +1378,27 @@
         <v>741</v>
       </c>
       <c r="G9" t="s">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="H9" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
-        <v>233</v>
+        <v>171</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>235</v>
+        <v>173</v>
       </c>
       <c r="E10">
         <v>4.4000000000000004</v>
@@ -1603,27 +1407,27 @@
         <v>1132</v>
       </c>
       <c r="G10" t="s">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="H10" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>243</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>244</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>183</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="E11">
         <v>4.2</v>
@@ -1632,27 +1436,27 @@
         <v>582</v>
       </c>
       <c r="G11" t="s">
-        <v>247</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="I11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>194</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>257</v>
+        <v>195</v>
       </c>
       <c r="E12">
         <v>4.3</v>
@@ -1661,27 +1465,27 @@
         <v>1853</v>
       </c>
       <c r="G12" t="s">
-        <v>258</v>
+        <v>196</v>
       </c>
       <c r="H12" t="s">
-        <v>259</v>
+        <v>197</v>
       </c>
       <c r="I12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>297</v>
+        <v>221</v>
       </c>
       <c r="E13">
         <v>4.4000000000000004</v>
@@ -1690,443 +1494,459 @@
         <v>1680</v>
       </c>
       <c r="G13" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
       <c r="H13" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="I13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14">
+        <v>4.7</v>
+      </c>
+      <c r="F14">
+        <v>398</v>
+      </c>
+      <c r="G14" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" t="s">
+        <v>228</v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B15" t="s">
+        <v>126</v>
+      </c>
+      <c r="C15" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15">
+        <v>4.3</v>
+      </c>
+      <c r="F15">
+        <v>380</v>
+      </c>
+      <c r="G15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" t="s">
+        <v>231</v>
+      </c>
+      <c r="I15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" t="s">
-        <v>12</v>
+        <v>132</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>133</v>
       </c>
       <c r="E16">
-        <v>4.9000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="F16">
-        <v>3347</v>
+        <v>658</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
+        <v>134</v>
+      </c>
+      <c r="H16" t="s">
+        <v>232</v>
       </c>
       <c r="I16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>18</v>
+        <v>158</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>234</v>
       </c>
       <c r="E17">
-        <v>4.5999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F17">
-        <v>1365</v>
+        <v>301</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>159</v>
+      </c>
+      <c r="H17" t="s">
+        <v>233</v>
       </c>
       <c r="I17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" t="s">
-        <v>30</v>
+        <v>178</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E18">
         <v>4.7</v>
       </c>
       <c r="F18">
+        <v>1145</v>
+      </c>
+      <c r="G18" t="s">
+        <v>180</v>
+      </c>
+      <c r="H18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19">
+        <v>4.2</v>
+      </c>
+      <c r="F19">
+        <v>4908</v>
+      </c>
+      <c r="G19" t="s">
+        <v>207</v>
+      </c>
+      <c r="H19" t="s">
+        <v>236</v>
+      </c>
+      <c r="I19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="F23">
+        <v>3347</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24">
+        <v>4.7</v>
+      </c>
+      <c r="F24">
         <v>367</v>
       </c>
-      <c r="G18" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>35</v>
-      </c>
-      <c r="E19">
-        <v>4.7</v>
-      </c>
-      <c r="F19">
-        <v>398</v>
-      </c>
-      <c r="G19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E20">
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25">
+        <v>4.5</v>
+      </c>
+      <c r="F25">
+        <v>1184</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F26">
+        <v>2822</v>
+      </c>
+      <c r="G26" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>230</v>
+      </c>
+      <c r="E27">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="F27">
+        <v>896</v>
+      </c>
+      <c r="G27" t="s">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28">
         <v>4.3</v>
       </c>
-      <c r="F20">
-        <v>3592</v>
-      </c>
-      <c r="G20" t="s">
-        <v>46</v>
-      </c>
-      <c r="I20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E21">
+      <c r="F28">
+        <v>2692</v>
+      </c>
+      <c r="G28" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" t="s">
+        <v>80</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29">
         <v>4.4000000000000004</v>
       </c>
-      <c r="F21">
-        <v>2466</v>
-      </c>
-      <c r="G21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
-      <c r="B22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22">
-        <v>4.2</v>
-      </c>
-      <c r="F22">
-        <v>2440</v>
-      </c>
-      <c r="G22" t="s">
-        <v>74</v>
-      </c>
-      <c r="I22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" t="s">
-        <v>76</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23">
-        <v>4.5</v>
-      </c>
-      <c r="F23">
-        <v>1184</v>
-      </c>
-      <c r="G23" t="s">
-        <v>79</v>
-      </c>
-      <c r="I23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="F29">
+        <v>1250</v>
+      </c>
+      <c r="G29" t="s">
+        <v>83</v>
+      </c>
+      <c r="I29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" t="s">
         <v>86</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D30" t="s">
         <v>87</v>
       </c>
-      <c r="C24" t="s">
+      <c r="E30">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="F30">
+        <v>2562</v>
+      </c>
+      <c r="G30" t="s">
         <v>88</v>
       </c>
-      <c r="D24" t="s">
+      <c r="I30" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>89</v>
       </c>
-      <c r="E24">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F24">
-        <v>203</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="B31" t="s">
         <v>90</v>
       </c>
-      <c r="I24" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="C31" t="s">
         <v>91</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D31" t="s">
         <v>92</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E31">
+        <v>4.3</v>
+      </c>
+      <c r="F31">
+        <v>1233</v>
+      </c>
+      <c r="G31" t="s">
         <v>93</v>
       </c>
-      <c r="D25" t="s">
+      <c r="I31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>94</v>
       </c>
-      <c r="E25">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F25">
-        <v>2822</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="B32" t="s">
         <v>95</v>
       </c>
-      <c r="I25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="C32" t="s">
         <v>96</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D32" t="s">
         <v>97</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E32">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F32">
+        <v>668</v>
+      </c>
+      <c r="G32" t="s">
         <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="F26">
-        <v>896</v>
-      </c>
-      <c r="G26" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" t="s">
-        <v>102</v>
-      </c>
-      <c r="C27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F27">
-        <v>1301</v>
-      </c>
-      <c r="G27" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="E28">
-        <v>4.7</v>
-      </c>
-      <c r="F28">
-        <v>218</v>
-      </c>
-      <c r="G28" t="s">
-        <v>108</v>
-      </c>
-      <c r="I28" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29">
-        <v>4.3</v>
-      </c>
-      <c r="F29">
-        <v>2692</v>
-      </c>
-      <c r="G29" t="s">
-        <v>113</v>
-      </c>
-      <c r="I29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F30">
-        <v>1250</v>
-      </c>
-      <c r="G30" t="s">
-        <v>118</v>
-      </c>
-      <c r="I30" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>119</v>
-      </c>
-      <c r="B31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C31" t="s">
-        <v>121</v>
-      </c>
-      <c r="D31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E31">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F31">
-        <v>2562</v>
-      </c>
-      <c r="G31" t="s">
-        <v>123</v>
-      </c>
-      <c r="I31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C32" t="s">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32">
-        <v>4.3</v>
-      </c>
-      <c r="F32">
-        <v>1233</v>
-      </c>
-      <c r="G32" t="s">
-        <v>128</v>
       </c>
       <c r="I32" t="s">
         <v>14</v>
@@ -2134,25 +1954,25 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="D33" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="E33">
-        <v>4.4000000000000004</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F33">
-        <v>668</v>
+        <v>15322</v>
       </c>
       <c r="G33" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="I33" t="s">
         <v>14</v>
@@ -2160,25 +1980,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E34">
-        <v>4.9000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F34">
-        <v>15322</v>
+        <v>720</v>
       </c>
       <c r="G34" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="I34" t="s">
         <v>14</v>
@@ -2186,22 +2006,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>117</v>
+      </c>
+      <c r="D35" t="s">
+        <v>118</v>
       </c>
       <c r="E35">
         <v>4.4000000000000004</v>
       </c>
       <c r="F35">
-        <v>554</v>
+        <v>854</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="I35" t="s">
         <v>14</v>
@@ -2209,25 +2032,25 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B36" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E36">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F36">
-        <v>657</v>
+        <v>4369</v>
       </c>
       <c r="G36" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
         <v>14</v>
@@ -2235,25 +2058,25 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="E37">
-        <v>4.5999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="F37">
-        <v>720</v>
+        <v>2112</v>
       </c>
       <c r="G37" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="I37" t="s">
         <v>14</v>
@@ -2261,25 +2084,25 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="C38" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E38">
-        <v>4.4000000000000004</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F38">
-        <v>854</v>
+        <v>1073</v>
       </c>
       <c r="G38" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="I38" t="s">
         <v>14</v>
@@ -2287,25 +2110,25 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C39" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E39">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F39">
-        <v>4369</v>
+        <v>1560</v>
       </c>
       <c r="G39" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="I39" t="s">
         <v>14</v>
@@ -2313,22 +2136,25 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C40" t="s">
-        <v>171</v>
+        <v>162</v>
+      </c>
+      <c r="D40" t="s">
+        <v>163</v>
       </c>
       <c r="E40">
-        <v>4.0999999999999996</v>
+        <v>4</v>
       </c>
       <c r="F40">
-        <v>1707</v>
+        <v>3472</v>
       </c>
       <c r="G40" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I40" t="s">
         <v>14</v>
@@ -2336,25 +2162,25 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D41" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E41">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>380</v>
+        <v>2248</v>
       </c>
       <c r="G41" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s">
         <v>14</v>
@@ -2362,22 +2188,25 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B42" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>189</v>
+      </c>
+      <c r="D42" t="s">
+        <v>190</v>
       </c>
       <c r="E42">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F42">
-        <v>849</v>
+        <v>1922</v>
       </c>
       <c r="G42" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="I42" t="s">
         <v>14</v>
@@ -2385,25 +2214,25 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E43">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="F43">
-        <v>658</v>
+        <v>952</v>
       </c>
       <c r="G43" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="I43" t="s">
         <v>14</v>
@@ -2411,25 +2240,25 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C44" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="D44" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="E44">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F44">
-        <v>2112</v>
+        <v>632</v>
       </c>
       <c r="G44" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="I44" t="s">
         <v>14</v>
@@ -2437,25 +2266,25 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C45" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="D45" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="E45">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="F45">
-        <v>472</v>
+        <v>1701</v>
       </c>
       <c r="G45" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="I45" t="s">
         <v>14</v>
@@ -2463,417 +2292,33 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D46" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="E46">
-        <v>4.5999999999999996</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="F46">
-        <v>1073</v>
+        <v>1272</v>
       </c>
       <c r="G46" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="I46" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>208</v>
-      </c>
-      <c r="B47" t="s">
-        <v>209</v>
-      </c>
-      <c r="C47" t="s">
-        <v>210</v>
-      </c>
-      <c r="E47">
-        <v>4.5</v>
-      </c>
-      <c r="F47">
-        <v>258</v>
-      </c>
-      <c r="G47" t="s">
-        <v>211</v>
-      </c>
-      <c r="I47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>212</v>
-      </c>
-      <c r="B48" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" t="s">
-        <v>214</v>
-      </c>
-      <c r="D48" t="s">
-        <v>215</v>
-      </c>
-      <c r="E48">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F48">
-        <v>1560</v>
-      </c>
-      <c r="G48" t="s">
-        <v>216</v>
-      </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>217</v>
-      </c>
-      <c r="B49" t="s">
-        <v>218</v>
-      </c>
-      <c r="C49" t="s">
-        <v>219</v>
-      </c>
-      <c r="D49" t="s">
-        <v>220</v>
-      </c>
-      <c r="E49">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F49">
-        <v>301</v>
-      </c>
-      <c r="G49" t="s">
-        <v>221</v>
-      </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>222</v>
-      </c>
-      <c r="B50" t="s">
-        <v>223</v>
-      </c>
-      <c r="C50" t="s">
-        <v>224</v>
-      </c>
-      <c r="D50" t="s">
-        <v>225</v>
-      </c>
-      <c r="E50">
-        <v>4</v>
-      </c>
-      <c r="F50">
-        <v>3472</v>
-      </c>
-      <c r="G50" t="s">
-        <v>226</v>
-      </c>
-      <c r="I50" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>227</v>
-      </c>
-      <c r="B51" t="s">
-        <v>228</v>
-      </c>
-      <c r="C51" t="s">
-        <v>229</v>
-      </c>
-      <c r="D51" t="s">
-        <v>230</v>
-      </c>
-      <c r="E51">
-        <v>4</v>
-      </c>
-      <c r="F51">
-        <v>2248</v>
-      </c>
-      <c r="G51" t="s">
-        <v>231</v>
-      </c>
-      <c r="I51" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>238</v>
-      </c>
-      <c r="B52" t="s">
-        <v>239</v>
-      </c>
-      <c r="C52" t="s">
-        <v>240</v>
-      </c>
-      <c r="D52" t="s">
-        <v>241</v>
-      </c>
-      <c r="E52">
-        <v>4.7</v>
-      </c>
-      <c r="F52">
-        <v>1145</v>
-      </c>
-      <c r="G52" t="s">
-        <v>242</v>
-      </c>
-      <c r="I52" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>249</v>
-      </c>
-      <c r="B53" t="s">
-        <v>250</v>
-      </c>
-      <c r="C53" t="s">
-        <v>251</v>
-      </c>
-      <c r="D53" t="s">
-        <v>252</v>
-      </c>
-      <c r="E53">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F53">
-        <v>1922</v>
-      </c>
-      <c r="G53" t="s">
-        <v>253</v>
-      </c>
-      <c r="I53" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" t="s">
-        <v>261</v>
-      </c>
-      <c r="C54" t="s">
-        <v>262</v>
-      </c>
-      <c r="E54">
-        <v>4.2</v>
-      </c>
-      <c r="F54">
-        <v>934</v>
-      </c>
-      <c r="G54" t="s">
-        <v>263</v>
-      </c>
-      <c r="I54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>264</v>
-      </c>
-      <c r="B55" t="s">
-        <v>265</v>
-      </c>
-      <c r="C55" t="s">
-        <v>266</v>
-      </c>
-      <c r="D55" t="s">
-        <v>267</v>
-      </c>
-      <c r="E55">
-        <v>4.3</v>
-      </c>
-      <c r="F55">
-        <v>1058</v>
-      </c>
-      <c r="G55" t="s">
-        <v>268</v>
-      </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>269</v>
-      </c>
-      <c r="B56" t="s">
-        <v>270</v>
-      </c>
-      <c r="C56" t="s">
-        <v>271</v>
-      </c>
-      <c r="D56" t="s">
-        <v>272</v>
-      </c>
-      <c r="E56">
-        <v>4.8</v>
-      </c>
-      <c r="F56">
-        <v>952</v>
-      </c>
-      <c r="G56" t="s">
-        <v>273</v>
-      </c>
-      <c r="I56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>274</v>
-      </c>
-      <c r="B57" t="s">
-        <v>275</v>
-      </c>
-      <c r="C57" t="s">
-        <v>276</v>
-      </c>
-      <c r="D57" t="s">
-        <v>277</v>
-      </c>
-      <c r="E57">
-        <v>4.2</v>
-      </c>
-      <c r="F57">
-        <v>4908</v>
-      </c>
-      <c r="G57" t="s">
-        <v>278</v>
-      </c>
-      <c r="I57" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>279</v>
-      </c>
-      <c r="B58" t="s">
-        <v>280</v>
-      </c>
-      <c r="C58" t="s">
-        <v>281</v>
-      </c>
-      <c r="D58" t="s">
-        <v>282</v>
-      </c>
-      <c r="E58">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="F58">
-        <v>632</v>
-      </c>
-      <c r="G58" t="s">
-        <v>283</v>
-      </c>
-      <c r="I58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>284</v>
-      </c>
-      <c r="B59" t="s">
-        <v>285</v>
-      </c>
-      <c r="C59" t="s">
-        <v>286</v>
-      </c>
-      <c r="D59" t="s">
-        <v>287</v>
-      </c>
-      <c r="E59">
-        <v>4</v>
-      </c>
-      <c r="F59">
-        <v>1701</v>
-      </c>
-      <c r="G59" t="s">
-        <v>288</v>
-      </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>289</v>
-      </c>
-      <c r="B60" t="s">
-        <v>290</v>
-      </c>
-      <c r="C60" t="s">
-        <v>291</v>
-      </c>
-      <c r="D60" t="s">
-        <v>292</v>
-      </c>
-      <c r="E60">
-        <v>4.2</v>
-      </c>
-      <c r="F60">
-        <v>946</v>
-      </c>
-      <c r="G60" t="s">
-        <v>293</v>
-      </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>300</v>
-      </c>
-      <c r="B61" t="s">
-        <v>301</v>
-      </c>
-      <c r="C61" t="s">
-        <v>302</v>
-      </c>
-      <c r="D61" t="s">
-        <v>303</v>
-      </c>
-      <c r="E61">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="F61">
-        <v>1272</v>
-      </c>
-      <c r="G61" t="s">
-        <v>304</v>
-      </c>
-      <c r="I61" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I61">
-    <sortCondition ref="I2:I61"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I46">
+    <sortCondition ref="I2:I46"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
